--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_388_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_388_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>51:22</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>28</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>50:57</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>39:25</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>40:26</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>30:01</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>34:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>27:15</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>19.7%</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
           <t>12.5%</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>7.9%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -2903,16 +2903,16 @@
         <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>4</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,17 +3019,17 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>3</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>27:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -3497,10 +3497,10 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>40:32</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>117</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>48:14</t>
+          <t>28:14</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>50:45</t>
+          <t>29:47</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>02:25</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>44:40</t>
+          <t>23:43</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>39:59</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>45:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>34:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>49:49</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -5860,16 +5860,16 @@
         <v>14</v>
       </c>
       <c r="T43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>4</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>48:51</t>
+          <t>28:50</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>29:17</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
     </row>
@@ -6392,16 +6392,16 @@
         <v>68</v>
       </c>
       <c r="T46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>18</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_388_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_388_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
         <v>11</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>11</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>4</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>3</v>
@@ -3497,10 +3497,10 @@
         <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
@@ -3827,16 +3827,16 @@
         <v>117</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -4488,7 +4488,7 @@
         <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5670,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>1</v>
@@ -5860,16 +5860,16 @@
         <v>14</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X43" t="n">
         <v>4</v>
@@ -6392,16 +6392,16 @@
         <v>68</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X46" t="n">
         <v>18</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_388_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_388_EL.xlsx
@@ -674,10 +674,10 @@
         <v>11</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -851,20 +851,20 @@
         <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -2327,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>2</v>
       </c>
       <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
         <v>4</v>
       </c>
-      <c r="Y25" t="n">
-        <v>5</v>
-      </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" t="n">
         <v>3</v>
       </c>
-      <c r="Y27" t="n">
-        <v>4</v>
-      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>8</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4337,25 +4337,25 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -5088,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6404,14 +6404,14 @@
         <v>3</v>
       </c>
       <c r="X46" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Y46" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6437,25 +6437,25 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK46" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
